--- a/Streamlit/Data/object_manual_published.xlsx
+++ b/Streamlit/Data/object_manual_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,6 +434,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Order</t>
         </is>
       </c>
@@ -454,7 +459,8 @@
           <t>Process Step</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -474,7 +480,8 @@
           <t>Relative Order</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -494,7 +501,8 @@
           <t>Column List</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -514,7 +522,8 @@
           <t>Material Change Log</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -534,7 +543,8 @@
           <t>Reference List</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -554,7 +564,8 @@
           <t>Reference String</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -574,128 +585,143 @@
           <t>Reference Dictionary</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Process Definition</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Default Categorization List Options for Objects, which assigns taxonmy to my Organizational Structure</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
+          <t>Homoscedasticity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
+          <t>Independence</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guiding Principle</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
+          <t>Linearity</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Guidance</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
+          <t>Normality</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Expected Outcomes</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>6</v>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>The Best Linear Unbiased Estimator (BLUE) is an estimation method in statistics that produces parameter estimates that are linear in the observed data, unbiased, and have the smallest possible variance among all such estimators. It originates from the Gauss–Markov theorem, developed in the early 19th century in the context of least squares and error theory. Its importance lies in providing a theoretical benchmark: under specific assumptions about error structure, no other linear unbiased estimator can be more precise. In practice, BLUE underpins ordinary and generalized least squares, and is widely applied in econometrics, engineering, and data science when modeling relationships with correlated or heteroskedastic errors</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -711,11 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -731,11 +758,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algorithm</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>8</v>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -751,151 +779,163 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>9</v>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
+          <t>Guiding Principle</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
+          <t>Expected Outcomes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Root Cause Analysis</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>5</v>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>6</v>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option Generation</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>7</v>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -911,11 +951,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Solution Design</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -931,11 +972,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>9</v>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -951,11 +993,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -971,11 +1014,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11</v>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -991,11 +1035,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>12</v>
+          <t>Root Cause Analysis</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1011,11 +1056,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>13</v>
+          <t>Research and Exploration</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1031,11 +1077,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>14</v>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1051,11 +1098,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Optimization</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>15</v>
+          <t>Solution Design</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1071,11 +1119,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>16</v>
+          <t>Feasibility Assessment</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -1091,11 +1140,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>17</v>
+          <t>Prioritization and Decision Making</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -1111,11 +1161,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>18</v>
+          <t>Implementation Planning</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="36">
@@ -1131,17 +1182,18 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Governance, Risk, and Ethics</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>19</v>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1151,17 +1203,18 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
+          <t>Testing and Validation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1171,17 +1224,18 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1191,17 +1245,18 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>3</v>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1211,17 +1266,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4</v>
+          <t>Documentation and Knowledge Sharing</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1231,17 +1287,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>5</v>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1251,17 +1308,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>6</v>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1271,31 +1329,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>7</v>
+          <t>Governance, Risk, and Ethics</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>8</v>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Structured approach to solving complex problems.</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -1311,11 +1375,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>9</v>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1331,11 +1396,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1351,11 +1417,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11</v>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1371,11 +1438,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>12</v>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -1391,11 +1459,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>13</v>
+          <t>Exploratory Data Analysis</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -1411,11 +1480,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>14</v>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -1431,11 +1501,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>15</v>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1451,191 +1522,205 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>16</v>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FINALNAME</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>COLUMN</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2</v>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>METRIC_TYPE</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>3</v>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>METRIC_CLASSIFICATION</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PRODUCT</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>5</v>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>6</v>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>METRIC</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>7</v>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>8</v>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RECORD_TYPE</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>9</v>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="62">
@@ -1651,11 +1736,226 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>FINALNAME</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>METRIC_TYPE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>METRIC_CLASSIFICATION</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PRODUCT</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>RECORD_TYPE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>UPDATE_DATE</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>List of Default Columns Used in Data Dictionary</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Streamlit/Data/object_manual_published.xlsx
+++ b/Streamlit/Data/object_manual_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -618,513 +618,517 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Homoscedasticity</t>
+          <t>function_purpose</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>parameters</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Linearity</t>
+          <t>date_created</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Normality</t>
+          <t>date_last_modified</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>The Best Linear Unbiased Estimator (BLUE) is an estimation method in statistics that produces parameter estimates that are linear in the observed data, unbiased, and have the smallest possible variance among all such estimators. It originates from the Gauss–Markov theorem, developed in the early 19th century in the context of least squares and error theory. Its importance lies in providing a theoretical benchmark: under specific assumptions about error structure, no other linear unbiased estimator can be more precise. In practice, BLUE underpins ordinary and generalized least squares, and is widely applied in econometrics, engineering, and data science when modeling relationships with correlated or heteroskedastic errors</t>
-        </is>
-      </c>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Process Definition</t>
+          <t>categorization</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>usage</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Guiding Principle</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Default Columns to be included and labelled when documenting personally created functions in Python</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Homoscedasticity</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Expected Outcomes</t>
+          <t>Independence</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Linearity</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Normality</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The Best Linear Unbiased Estimator (BLUE) is an estimation method in statistics that produces parameter estimates that are linear in the observed data, unbiased, and have the smallest possible variance among all such estimators. It originates from the Gauss–Markov theorem, developed in the early 19th century in the context of least squares and error theory. Its importance lies in providing a theoretical benchmark: under specific assumptions about error structure, no other linear unbiased estimator can be more precise. In practice, BLUE underpins ordinary and generalized least squares, and is widely applied in econometrics, engineering, and data science when modeling relationships with correlated or heteroskedastic errors</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
-        </is>
-      </c>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
+          <t>Guiding Principle</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Root Cause Analysis</t>
+          <t>Expected Outcomes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option Generation</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -1140,12 +1144,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1161,12 +1165,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1182,12 +1186,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Current State Assessment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1203,12 +1207,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1224,12 +1228,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -1245,12 +1249,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Research and Exploration</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -1266,12 +1270,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Option Generation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1287,12 +1291,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Solution Design</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1308,12 +1312,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -1329,12 +1333,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Governance, Risk, and Ethics</t>
+          <t>Prioritization and Decision Making</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -1345,27 +1349,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Structured approach to solving complex problems.</t>
-        </is>
-      </c>
+          <t>Implementation Planning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1375,18 +1375,18 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1396,18 +1396,18 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1417,18 +1417,18 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1438,18 +1438,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1459,18 +1459,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1480,18 +1480,18 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1501,18 +1501,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Continuous Improvement</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1522,33 +1522,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Structured approach to solving complex problems.</t>
+        </is>
+      </c>
       <c r="E53" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -1564,12 +1568,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1585,12 +1589,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1606,12 +1610,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1627,12 +1631,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -1648,12 +1652,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -1669,12 +1673,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -1690,12 +1694,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1706,216 +1710,216 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FINALNAME</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>COLUMN</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>METRIC_TYPE</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>METRIC_CLASSIFICATION</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PRODUCT</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>METRIC</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NOTES</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RECORD_TYPE</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
+        </is>
+      </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1925,37 +1929,226 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UPDATE_DATE</t>
+          <t>FINALNAME</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Dictionary</t>
+          <t>Organziation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>METRIC_TYPE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>METRIC_CLASSIFICATION</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PRODUCT</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>RECORD_TYPE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>UPDATE_DATE</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Organziation</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>List of Default Columns Used in Data Dictionary</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>11</v>
+      <c r="E81" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Streamlit/Data/object_manual_published.xlsx
+++ b/Streamlit/Data/object_manual_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -467,7 +467,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Relative Order</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Returns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -509,7 +509,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Material Change Log</t>
+          <t>Date Created</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Date Last Modified</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -551,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reference String</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -572,7 +572,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reference Dictionary</t>
+          <t>Categorization</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -593,24 +593,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Default Categorization List Options for Objects, which assigns taxonmy to my Organizational Structure</t>
-        </is>
-      </c>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>8</v>
       </c>
@@ -618,7 +614,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -628,7 +624,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>function_purpose</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -639,20 +635,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>parameters</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Default Columns to be included and labelled when documenting personally created functions in Python</t>
+        </is>
+      </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
@@ -660,267 +660,263 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date_created</t>
+          <t>Homoscedasticity</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date_last_modified</t>
+          <t>Independence</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>Linearity</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>categorization</t>
+          <t>Normality</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usage</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The Best Linear Unbiased Estimator (BLUE) is an estimation method in statistics that produces parameter estimates that are linear in the observed data, unbiased, and have the smallest possible variance among all such estimators. It originates from the Gauss–Markov theorem, developed in the early 19th century in the context of least squares and error theory. Its importance lies in providing a theoretical benchmark: under specific assumptions about error structure, no other linear unbiased estimator can be more precise. In practice, BLUE underpins ordinary and generalized least squares, and is widely applied in econometrics, engineering, and data science when modeling relationships with correlated or heteroskedastic errors</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Process Definition</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Filter Order</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Default Columns to be included and labelled when documenting personally created functions in Python</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Homoscedasticity</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>Guiding Principle</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Linearity</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Normality</t>
+          <t>Expected Outcomes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>The Best Linear Unbiased Estimator (BLUE) is an estimation method in statistics that produces parameter estimates that are linear in the observed data, unbiased, and have the smallest possible variance among all such estimators. It originates from the Gauss–Markov theorem, developed in the early 19th century in the context of least squares and error theory. Its importance lies in providing a theoretical benchmark: under specific assumptions about error structure, no other linear unbiased estimator can be more precise. In practice, BLUE underpins ordinary and generalized least squares, and is widely applied in econometrics, engineering, and data science when modeling relationships with correlated or heteroskedastic errors</t>
-        </is>
-      </c>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -930,18 +926,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Process Definition</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -951,184 +947,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Guiding Principle</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Expected Outcomes</t>
+          <t>Current State Assessment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Research and Exploration</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
-        </is>
-      </c>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1144,12 +1140,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Solution Design</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1165,12 +1161,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -1186,12 +1182,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
+          <t>Prioritization and Decision Making</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1207,12 +1203,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -1228,12 +1224,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Root Cause Analysis</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -1249,12 +1245,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -1270,12 +1266,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Option Generation</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
@@ -1291,12 +1287,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -1312,12 +1308,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -1333,12 +1329,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
@@ -1354,12 +1350,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
+          <t>Continuous Improvement</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -1375,12 +1371,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -1391,23 +1387,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Structured approach to solving complex problems.</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1417,18 +1417,18 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1438,18 +1438,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1459,18 +1459,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1480,18 +1480,18 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1501,18 +1501,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1522,37 +1522,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Governance, Risk, and Ethics</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Structured approach to solving complex problems.</t>
-        </is>
-      </c>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1568,12 +1564,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1589,12 +1585,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -1610,12 +1606,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -1631,12 +1627,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
@@ -1652,12 +1648,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -1673,12 +1669,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -1694,12 +1690,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -1715,12 +1711,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -1736,12 +1732,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -1752,403 +1748,256 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
+        </is>
+      </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>FINALNAME</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>COLUMN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>METRIC_TYPE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>METRIC_CLASSIFICATION</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>PRODUCT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>DESCRIPTION</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
-        </is>
-      </c>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FINALNAME</t>
+          <t>NOTES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>COLUMN</t>
+          <t>RECORD_TYPE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>METRIC_TYPE</t>
+          <t>UPDATE_DATE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Organziation</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>METRIC_CLASSIFICATION</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>List of Default Columns Used in Data Dictionary</t>
+        </is>
+      </c>
       <c r="E74" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Organziation</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Column List</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>PRODUCT</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Organziation</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Column List</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Organziation</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Column List</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>METRIC</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Organziation</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Column List</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Organziation</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Column List</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>RECORD_TYPE</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Organziation</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Column List</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>UPDATE_DATE</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Organziation</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>List of Default Columns Used in Data Dictionary</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Streamlit/Data/object_manual_published.xlsx
+++ b/Streamlit/Data/object_manual_published.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,7 +842,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Guiding Principle</t>
+          <t>Reqiurement</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Guiding Principle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -884,7 +884,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Expected Outcomes</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Expected Outcomes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -963,19 +963,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
-        </is>
-      </c>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>10</v>
       </c>
@@ -983,22 +979,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
+        </is>
+      </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Current State Assessment</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Root Cause Analysis</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Option Generation</t>
+          <t>Research and Exploration</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Option Generation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Solution Design</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
+          <t>Prioritization and Decision Making</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Governance, Risk, and Ethics</t>
+          <t>Continuous Improvement</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
@@ -1387,42 +1387,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Structured approach to solving complex problems.</t>
-        </is>
-      </c>
+          <t>Governance, Risk, and Ethics</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Structured approach to solving complex problems.</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -1748,42 +1748,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
-        </is>
-      </c>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Dictionary Columns</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FINALNAME</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
+        </is>
+      </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>COLUMN</t>
+          <t>FINALNAME</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>METRIC_TYPE</t>
+          <t>COLUMN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>METRIC_CLASSIFICATION</t>
+          <t>METRIC_TYPE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PRODUCT</t>
+          <t>METRIC_CLASSIFICATION</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
+          <t>PRODUCT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>METRIC</t>
+          <t>DESCRIPTION</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NOTES</t>
+          <t>METRIC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RECORD_TYPE</t>
+          <t>NOTES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UPDATE_DATE</t>
+          <t>RECORD_TYPE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -1983,20 +1983,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UPDATE_DATE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>List of Default Columns Used in Data Dictionary</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E75" t="n">
         <v>11</v>
       </c>
     </row>
